--- a/data/trans_orig/P13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2007</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>526163</t>
+          <t>526055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>567704</t>
+          <t>568779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454126</t>
+          <t>454968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>501583</t>
+          <t>502589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>993273</t>
+          <t>996030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1057507</t>
+          <t>1057024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>66530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>99338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107874</t>
+          <t>107868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146135</t>
+          <t>147376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184669</t>
+          <t>183209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237885</t>
+          <t>234190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>38450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67894</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55256</t>
+          <t>54263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86193</t>
+          <t>85586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102010</t>
+          <t>101056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>142830</t>
+          <t>141257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>742945</t>
+          <t>742428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>790970</t>
+          <t>793648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>645003</t>
+          <t>644046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>700800</t>
+          <t>701920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1402642</t>
+          <t>1400747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1476695</t>
+          <t>1476870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>66927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103811</t>
+          <t>104838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98058</t>
+          <t>99535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139178</t>
+          <t>141463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178071</t>
+          <t>177141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232884</t>
+          <t>231720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54124</t>
+          <t>54923</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85996</t>
+          <t>89538</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114179</t>
+          <t>114489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160812</t>
+          <t>159080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178985</t>
+          <t>178083</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>230515</t>
+          <t>231301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30567</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62691</t>
+          <t>63531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28148</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>49062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>537197</t>
+          <t>536799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>576465</t>
+          <t>576833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>457421</t>
+          <t>458755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>504163</t>
+          <t>505682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1004703</t>
+          <t>1009760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1068873</t>
+          <t>1072733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77080</t>
+          <t>78311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>72287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105332</t>
+          <t>107256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128938</t>
+          <t>126040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176491</t>
+          <t>171902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50571</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61496</t>
+          <t>60417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91452</t>
+          <t>92980</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95017</t>
+          <t>96214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135014</t>
+          <t>133910</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36768</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26561</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14739</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>689742</t>
+          <t>689839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>740551</t>
+          <t>742472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>675249</t>
+          <t>677377</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>735233</t>
+          <t>740524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1383267</t>
+          <t>1378816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1461465</t>
+          <t>1462324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92980</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135368</t>
+          <t>132285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>101080</t>
+          <t>103562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144688</t>
+          <t>144947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208108</t>
+          <t>208101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>267726</t>
+          <t>267401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68117</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101601</t>
+          <t>102623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114842</t>
+          <t>115210</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>159578</t>
+          <t>159366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>195411</t>
+          <t>192700</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>250341</t>
+          <t>247914</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50943</t>
+          <t>50468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35060</t>
+          <t>36094</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63099</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23567</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>39774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67439</t>
+          <t>68668</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2539020</t>
+          <t>2540627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2633213</t>
+          <t>2635958</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2290260</t>
+          <t>2283746</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2396815</t>
+          <t>2395384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4857636</t>
+          <t>4849839</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5015093</t>
+          <t>5000034</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>304612</t>
+          <t>306729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>377710</t>
+          <t>378425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>423187</t>
+          <t>417314</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>502339</t>
+          <t>499032</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>742152</t>
+          <t>747885</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>849983</t>
+          <t>852255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>214391</t>
+          <t>213165</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>271492</t>
+          <t>271724</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>377213</t>
+          <t>379230</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>459638</t>
+          <t>454774</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>607867</t>
+          <t>609731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>704473</t>
+          <t>709470</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>69506</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>78724</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>117139</t>
+          <t>118784</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>125915</t>
+          <t>127698</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>175544</t>
+          <t>173915</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>39909</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67311</t>
+          <t>70377</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>51183</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>97861</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>145389</t>
+          <t>142815</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2012</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500049</t>
+          <t>498941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>544125</t>
+          <t>546395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>398834</t>
+          <t>397450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>453223</t>
+          <t>449900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>914880</t>
+          <t>912376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>985411</t>
+          <t>983465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82955</t>
+          <t>82041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120149</t>
+          <t>118553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133693</t>
+          <t>132069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186201</t>
+          <t>184232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239780</t>
+          <t>240151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32610</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58195</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68364</t>
+          <t>68041</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101631</t>
+          <t>102343</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107927</t>
+          <t>108173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>153498</t>
+          <t>151689</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>37079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>57668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>49625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84903</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48009</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61622</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>732816</t>
+          <t>733151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>789772</t>
+          <t>792890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>606664</t>
+          <t>607683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>673451</t>
+          <t>673320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1362822</t>
+          <t>1357066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1448499</t>
+          <t>1444358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97459</t>
+          <t>97508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140676</t>
+          <t>140345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131096</t>
+          <t>130140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178602</t>
+          <t>181127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245431</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306157</t>
+          <t>306937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71002</t>
+          <t>70300</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109612</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>128647</t>
+          <t>129819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174998</t>
+          <t>174924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>208614</t>
+          <t>209394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269303</t>
+          <t>270157</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>45251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67206</t>
+          <t>69716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>67020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104288</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28148</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>65081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>569558</t>
+          <t>571446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>619130</t>
+          <t>618833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>500635</t>
+          <t>501367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>554206</t>
+          <t>554791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1086734</t>
+          <t>1083592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1154619</t>
+          <t>1158095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86388</t>
+          <t>85390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>71614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107634</t>
+          <t>109026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133331</t>
+          <t>135981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182046</t>
+          <t>185767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46377</t>
+          <t>49050</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80363</t>
+          <t>81125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113573</t>
+          <t>114366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134128</t>
+          <t>132602</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180081</t>
+          <t>184120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31190</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30818</t>
+          <t>29734</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56304</t>
+          <t>57465</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>47359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79168</t>
+          <t>79140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>21100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50806</t>
+          <t>49458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>658568</t>
+          <t>661384</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>719213</t>
+          <t>718392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>616536</t>
+          <t>613682</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>681155</t>
+          <t>678363</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1291255</t>
+          <t>1294427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1383548</t>
+          <t>1381885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95054</t>
+          <t>95567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139039</t>
+          <t>138785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>141496</t>
+          <t>142904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>191691</t>
+          <t>190125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>249511</t>
+          <t>250560</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>314398</t>
+          <t>317014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77972</t>
+          <t>78084</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117234</t>
+          <t>114731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111703</t>
+          <t>112146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155626</t>
+          <t>156876</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>201387</t>
+          <t>200847</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>256760</t>
+          <t>261232</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23326</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45741</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>56964</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91017</t>
+          <t>90216</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84373</t>
+          <t>84467</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127887</t>
+          <t>126211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>22646</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>58437</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2517910</t>
+          <t>2516950</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2622952</t>
+          <t>2626310</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2186797</t>
+          <t>2187840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2305389</t>
+          <t>2301056</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4738862</t>
+          <t>4735479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4896951</t>
+          <t>4892044</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>362925</t>
+          <t>362241</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>438920</t>
+          <t>443138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>478514</t>
+          <t>481708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>564754</t>
+          <t>564317</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>861503</t>
+          <t>862477</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>979281</t>
+          <t>982903</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>259120</t>
+          <t>260844</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>330008</t>
+          <t>327652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>424055</t>
+          <t>420258</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>505001</t>
+          <t>499277</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>704244</t>
+          <t>704020</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>807748</t>
+          <t>811665</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>89732</t>
+          <t>88224</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>132766</t>
+          <t>131617</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>180259</t>
+          <t>181259</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>235520</t>
+          <t>242003</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>281953</t>
+          <t>283161</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>355979</t>
+          <t>352976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67295</t>
+          <t>66239</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>101344</t>
+          <t>102264</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>148965</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>145697</t>
+          <t>148547</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>201222</t>
+          <t>204565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2016</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>525497</t>
+          <t>524619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>567207</t>
+          <t>565752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>464850</t>
+          <t>464376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>511534</t>
+          <t>510090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>998262</t>
+          <t>1001203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1061072</t>
+          <t>1065281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83618</t>
+          <t>83626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64136</t>
+          <t>64172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97503</t>
+          <t>97605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123957</t>
+          <t>124622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170574</t>
+          <t>172045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,82 +8258,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>60172</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>46554</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>77735</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>94305</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>77543</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>116299</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>7,01%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60172</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>46473</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75687</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>94305</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>76071</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>114770</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>27112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>52661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>775694</t>
+          <t>775644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>827614</t>
+          <t>825061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>693634</t>
+          <t>694094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>754666</t>
+          <t>755522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1483235</t>
+          <t>1485945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1565999</t>
+          <t>1569077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115787</t>
+          <t>117018</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158587</t>
+          <t>160660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137953</t>
+          <t>137623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183450</t>
+          <t>186847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265011</t>
+          <t>263462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333040</t>
+          <t>329414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41097</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69103</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91083</t>
+          <t>89918</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132152</t>
+          <t>131633</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>140552</t>
+          <t>140725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>193504</t>
+          <t>192983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28890</t>
+          <t>28933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41352</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>63457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37888</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>545995</t>
+          <t>547778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>596261</t>
+          <t>598902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>483285</t>
+          <t>479391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>533212</t>
+          <t>538654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1046255</t>
+          <t>1047715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1118480</t>
+          <t>1121537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92506</t>
+          <t>92526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134314</t>
+          <t>135167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112796</t>
+          <t>111475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152795</t>
+          <t>154886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216359</t>
+          <t>215234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274513</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84347</t>
+          <t>84836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>121627</t>
+          <t>123511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126268</t>
+          <t>123883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>172481</t>
+          <t>174574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54563</t>
+          <t>55297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>710013</t>
+          <t>710279</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>759105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>713218</t>
+          <t>711443</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>774169</t>
+          <t>775588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1436797</t>
+          <t>1433343</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1517132</t>
+          <t>1520049</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82214</t>
+          <t>84613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119441</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140504</t>
+          <t>141437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190091</t>
+          <t>190630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250757</t>
+          <t>248916</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81318</t>
+          <t>82637</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93123</t>
+          <t>92250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>134604</t>
+          <t>135723</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>155025</t>
+          <t>154684</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>209158</t>
+          <t>207497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31933</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67368</t>
+          <t>66261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54301</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2607559</t>
+          <t>2604960</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2701977</t>
+          <t>2703939</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2406564</t>
+          <t>2406408</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2522486</t>
+          <t>2523372</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5053706</t>
+          <t>5051570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5203568</t>
+          <t>5201477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>381233</t>
+          <t>384808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>457849</t>
+          <t>463842</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>451555</t>
+          <t>452118</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>534873</t>
+          <t>536810</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>852451</t>
+          <t>851714</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>961184</t>
+          <t>961764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170886</t>
+          <t>174081</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>230743</t>
+          <t>229818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>350870</t>
+          <t>348290</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>428776</t>
+          <t>426494</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>535122</t>
+          <t>541174</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>636214</t>
+          <t>636864</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>85131</t>
+          <t>86192</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>106990</t>
+          <t>106856</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>152495</t>
+          <t>153550</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>169348</t>
+          <t>169682</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>230449</t>
+          <t>226571</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>35446</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>64628</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>51403</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>85375</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>95592</t>
+          <t>93627</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>140581</t>
+          <t>139525</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2023</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>464935</t>
+          <t>464057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>505053</t>
+          <t>505687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>453225</t>
+          <t>454171</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>492836</t>
+          <t>492080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>930672</t>
+          <t>933302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>986798</t>
+          <t>987806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>38735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62100</t>
+          <t>63871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>54461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77997</t>
+          <t>76973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99904</t>
+          <t>98502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136393</t>
+          <t>132925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46247</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74543</t>
+          <t>73703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74489</t>
+          <t>74313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101250</t>
+          <t>102319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126421</t>
+          <t>126668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166349</t>
+          <t>164078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>28413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36412</t>
+          <t>35774</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>37801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60109</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29615</t>
+          <t>29230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>51172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>939864</t>
+          <t>943957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1085409</t>
+          <t>1101551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>627815</t>
+          <t>628125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>676348</t>
+          <t>675727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1576107</t>
+          <t>1578427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1811460</t>
+          <t>1834700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>40377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114975</t>
+          <t>112821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95831</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>125625</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129877</t>
+          <t>133217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228873</t>
+          <t>229514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35909</t>
+          <t>36101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95559</t>
+          <t>96501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108415</t>
+          <t>106886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145436</t>
+          <t>143296</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137441</t>
+          <t>123079</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>232903</t>
+          <t>231652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>39229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50280</t>
+          <t>50873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44121</t>
+          <t>43573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82872</t>
+          <t>82219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54016</t>
+          <t>52986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>503258</t>
+          <t>502731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>552238</t>
+          <t>550698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287343</t>
+          <t>224189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>670903</t>
+          <t>671201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>684417</t>
+          <t>716975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1205943</t>
+          <t>1206129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>60397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>94644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89657</t>
+          <t>90056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>561789</t>
+          <t>634370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165890</t>
+          <t>166030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>781457</t>
+          <t>766490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47683</t>
+          <t>48745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81956</t>
+          <t>80412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49389</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123902</t>
+          <t>120308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98788</t>
+          <t>103615</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>183362</t>
+          <t>184004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35357</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38574</t>
+          <t>37875</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>32257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>65622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>34070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>47245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>702325</t>
+          <t>698452</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>753228</t>
+          <t>748523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>731365</t>
+          <t>729561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>829084</t>
+          <t>825730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1446107</t>
+          <t>1448395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1553559</t>
+          <t>1549914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55635</t>
+          <t>56370</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88458</t>
+          <t>86507</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93434</t>
+          <t>94564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137926</t>
+          <t>136390</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>160869</t>
+          <t>162042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>212408</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58634</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>91247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100485</t>
+          <t>100181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>149896</t>
+          <t>150597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172112</t>
+          <t>172450</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>231603</t>
+          <t>230517</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39743</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>64708</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65617</t>
+          <t>65846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97205</t>
+          <t>96488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43747</t>
+          <t>44771</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>77373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2669774</t>
+          <t>2671044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2912578</t>
+          <t>2918715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1923406</t>
+          <t>1982924</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2571520</t>
+          <t>2571192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4636917</t>
+          <t>4627234</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5376734</t>
+          <t>5366310</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>222421</t>
+          <t>216712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>319109</t>
+          <t>319419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>377736</t>
+          <t>379350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1171244</t>
+          <t>1091992</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>640039</t>
+          <t>643970</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1465569</t>
+          <t>1530103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>205683</t>
+          <t>204150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>305160</t>
+          <t>304368</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>353081</t>
+          <t>347715</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>474695</t>
+          <t>473990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>597138</t>
+          <t>597898</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>755327</t>
+          <t>759706</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119886</t>
+          <t>119573</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>118593</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>167472</t>
+          <t>170417</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>208805</t>
+          <t>210406</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>273837</t>
+          <t>278128</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>51142</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88752</t>
+          <t>88136</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>83850</t>
+          <t>81720</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>122812</t>
+          <t>120743</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>146919</t>
+          <t>146578</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>200764</t>
+          <t>199342</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>526055</t>
+          <t>526240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>568779</t>
+          <t>568005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454968</t>
+          <t>453907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>502589</t>
+          <t>500295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>996030</t>
+          <t>991464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1057024</t>
+          <t>1057904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66530</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99338</t>
+          <t>99167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107868</t>
+          <t>107831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147376</t>
+          <t>148549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183209</t>
+          <t>184859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234190</t>
+          <t>237366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38450</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66121</t>
+          <t>65521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54263</t>
+          <t>54164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85586</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>101056</t>
+          <t>101033</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>141257</t>
+          <t>143786</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>742428</t>
+          <t>743356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>793648</t>
+          <t>791673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>644046</t>
+          <t>644313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>701920</t>
+          <t>702610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1400747</t>
+          <t>1402975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1476870</t>
+          <t>1476761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>67819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104838</t>
+          <t>102377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99535</t>
+          <t>99048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141463</t>
+          <t>140392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177141</t>
+          <t>178913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231720</t>
+          <t>232917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54923</t>
+          <t>54237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89538</t>
+          <t>87965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114489</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159080</t>
+          <t>159139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178083</t>
+          <t>180011</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>231301</t>
+          <t>232099</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>60624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>48137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>536799</t>
+          <t>536841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>576833</t>
+          <t>575301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>458755</t>
+          <t>461272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>505682</t>
+          <t>505129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1009760</t>
+          <t>1008270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1072733</t>
+          <t>1068129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78311</t>
+          <t>78275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72287</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107256</t>
+          <t>106649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126040</t>
+          <t>129462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171902</t>
+          <t>172798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60417</t>
+          <t>60781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92980</t>
+          <t>93207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>96214</t>
+          <t>94475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133910</t>
+          <t>134973</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26710</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50808</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34690</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>689839</t>
+          <t>687975</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>742472</t>
+          <t>739772</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>677377</t>
+          <t>675663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>740524</t>
+          <t>736577</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1378816</t>
+          <t>1378740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1462324</t>
+          <t>1463576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132285</t>
+          <t>133570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103562</t>
+          <t>104123</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144947</t>
+          <t>146377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208101</t>
+          <t>209600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>267401</t>
+          <t>265511</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67521</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102623</t>
+          <t>100950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115210</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>159366</t>
+          <t>159287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>192700</t>
+          <t>194451</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>247914</t>
+          <t>252055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>50585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36094</t>
+          <t>36657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63316</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28835</t>
+          <t>29085</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>47413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39774</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68668</t>
+          <t>68595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2540627</t>
+          <t>2542975</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2635958</t>
+          <t>2633610</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2283746</t>
+          <t>2291462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2395384</t>
+          <t>2397494</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4849839</t>
+          <t>4857284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5000034</t>
+          <t>5005205</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>306729</t>
+          <t>304799</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>378425</t>
+          <t>377540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>417314</t>
+          <t>416053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>499032</t>
+          <t>497395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>747885</t>
+          <t>745396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>852255</t>
+          <t>853345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>213165</t>
+          <t>214118</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>271724</t>
+          <t>274003</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>379230</t>
+          <t>376096</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>454774</t>
+          <t>451334</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>609731</t>
+          <t>608345</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>709470</t>
+          <t>705799</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>68329</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>78724</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>118784</t>
+          <t>117156</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>127698</t>
+          <t>126753</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>173915</t>
+          <t>175340</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39909</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70377</t>
+          <t>68449</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51183</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>84447</t>
+          <t>84286</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,47 +3963,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>118771</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>100626</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>144150</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>118771</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>97861</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>142815</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>498941</t>
+          <t>498781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>546395</t>
+          <t>545458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397450</t>
+          <t>396669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>449900</t>
+          <t>449190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>912376</t>
+          <t>915257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>983465</t>
+          <t>984204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118553</t>
+          <t>119341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93054</t>
+          <t>91060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132069</t>
+          <t>132151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184232</t>
+          <t>184021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240151</t>
+          <t>235391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59984</t>
+          <t>59794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68041</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102343</t>
+          <t>103021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108173</t>
+          <t>108860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151689</t>
+          <t>152318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37079</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57668</t>
+          <t>56496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49625</t>
+          <t>49357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>81490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46719</t>
+          <t>46945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>34655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60589</t>
+          <t>61616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>733151</t>
+          <t>731865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>792890</t>
+          <t>791623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607683</t>
+          <t>605732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>673320</t>
+          <t>670977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1357066</t>
+          <t>1360107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1444358</t>
+          <t>1443777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97508</t>
+          <t>96726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140345</t>
+          <t>138600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130140</t>
+          <t>134486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181127</t>
+          <t>180685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242337</t>
+          <t>243433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306937</t>
+          <t>307106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70300</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107634</t>
+          <t>108508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129819</t>
+          <t>128926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174924</t>
+          <t>173400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209394</t>
+          <t>209821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>270157</t>
+          <t>271363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45251</t>
+          <t>44630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69716</t>
+          <t>68304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67020</t>
+          <t>67857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103680</t>
+          <t>104078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22277</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45086</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36828</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>65425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>571446</t>
+          <t>568240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>618833</t>
+          <t>619274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>501367</t>
+          <t>502285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>554791</t>
+          <t>555691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1083592</t>
+          <t>1086189</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1158095</t>
+          <t>1160170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53549</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85390</t>
+          <t>86498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71614</t>
+          <t>69452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109026</t>
+          <t>106744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135981</t>
+          <t>135072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185767</t>
+          <t>184141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49050</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81125</t>
+          <t>82852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75099</t>
+          <t>76294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>111844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132602</t>
+          <t>131521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184120</t>
+          <t>183500</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>57486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47359</t>
+          <t>46698</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79140</t>
+          <t>76893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49458</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>661384</t>
+          <t>660486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>718392</t>
+          <t>716544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>613682</t>
+          <t>616293</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>678363</t>
+          <t>678761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1294427</t>
+          <t>1296090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1381885</t>
+          <t>1381400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95567</t>
+          <t>95918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138785</t>
+          <t>139622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142904</t>
+          <t>142721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>190125</t>
+          <t>188780</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250560</t>
+          <t>249545</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>317014</t>
+          <t>314061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78084</t>
+          <t>78351</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114731</t>
+          <t>114839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112146</t>
+          <t>111467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156876</t>
+          <t>158903</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200847</t>
+          <t>202381</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>261232</t>
+          <t>258982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>47316</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90216</t>
+          <t>91503</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84467</t>
+          <t>86028</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126211</t>
+          <t>128199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>46230</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58437</t>
+          <t>59736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2516950</t>
+          <t>2521602</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2626310</t>
+          <t>2626958</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2187840</t>
+          <t>2184000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2301056</t>
+          <t>2305126</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4735479</t>
+          <t>4723744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4892044</t>
+          <t>4889279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>362241</t>
+          <t>360517</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>443138</t>
+          <t>442284</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>481708</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>564317</t>
+          <t>564783</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>862477</t>
+          <t>865282</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>982903</t>
+          <t>980125</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>260844</t>
+          <t>260734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>327652</t>
+          <t>329905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>420258</t>
+          <t>418698</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>499277</t>
+          <t>502357</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>704020</t>
+          <t>700856</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>811665</t>
+          <t>807432</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>88224</t>
+          <t>89611</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>131617</t>
+          <t>132417</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>181259</t>
+          <t>180580</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>242003</t>
+          <t>236871</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,47 +7492,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>316074</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>280244</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>355803</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>5,1%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>316074</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>283161</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>352976</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>66239</t>
+          <t>67874</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>102264</t>
+          <t>103390</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>148939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>148547</t>
+          <t>148774</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>204565</t>
+          <t>204889</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>524619</t>
+          <t>527570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>565752</t>
+          <t>567655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>464376</t>
+          <t>464381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>510090</t>
+          <t>510414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1001203</t>
+          <t>1003483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1065281</t>
+          <t>1065900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83626</t>
+          <t>83920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64172</t>
+          <t>64686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97605</t>
+          <t>99810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124622</t>
+          <t>127478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172045</t>
+          <t>173704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77735</t>
+          <t>75199</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77543</t>
+          <t>76712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116299</t>
+          <t>115775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52661</t>
+          <t>52200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32150</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43917</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>775644</t>
+          <t>774690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>825061</t>
+          <t>827051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>694094</t>
+          <t>695310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>755522</t>
+          <t>754838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1485945</t>
+          <t>1486501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1569077</t>
+          <t>1568017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117018</t>
+          <t>115721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160660</t>
+          <t>160773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137623</t>
+          <t>137918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186847</t>
+          <t>185561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263462</t>
+          <t>266413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329414</t>
+          <t>328781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40784</t>
+          <t>41407</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69889</t>
+          <t>70688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89918</t>
+          <t>91451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>132570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>140725</t>
+          <t>138306</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192983</t>
+          <t>192207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41032</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>34006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>62400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>27883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38767</t>
+          <t>38686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>547778</t>
+          <t>547644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>598902</t>
+          <t>597499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>479391</t>
+          <t>481112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>538654</t>
+          <t>535667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1047715</t>
+          <t>1048250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1121537</t>
+          <t>1119809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92526</t>
+          <t>92723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135167</t>
+          <t>133842</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111475</t>
+          <t>111853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154886</t>
+          <t>156281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215234</t>
+          <t>217100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274062</t>
+          <t>273397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>62283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84836</t>
+          <t>85312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123511</t>
+          <t>122396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123883</t>
+          <t>128407</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174574</t>
+          <t>176393</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>40283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>40032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>710279</t>
+          <t>707579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>759105</t>
+          <t>758952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>711443</t>
+          <t>711438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>775588</t>
+          <t>774078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1433343</t>
+          <t>1437220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1520049</t>
+          <t>1517479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84613</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>122896</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98363</t>
+          <t>99672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141437</t>
+          <t>142710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190630</t>
+          <t>193712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>248916</t>
+          <t>250408</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50177</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82637</t>
+          <t>82368</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>92250</t>
+          <t>93767</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135723</t>
+          <t>137907</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>153003</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>207497</t>
+          <t>206452</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>31746</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>54811</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89792</t>
+          <t>91487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25209</t>
+          <t>26935</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2604960</t>
+          <t>2605606</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2703939</t>
+          <t>2703801</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2406408</t>
+          <t>2409965</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2523372</t>
+          <t>2521611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5051570</t>
+          <t>5044509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5201477</t>
+          <t>5194803</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>384808</t>
+          <t>380698</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>463842</t>
+          <t>460576</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>452118</t>
+          <t>448533</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>536810</t>
+          <t>537479</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>851714</t>
+          <t>856270</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>961764</t>
+          <t>967336</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174081</t>
+          <t>172647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>229818</t>
+          <t>228328</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>348290</t>
+          <t>346323</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>426494</t>
+          <t>425073</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>541174</t>
+          <t>543393</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>636864</t>
+          <t>638556</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>54070</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>88811</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>106856</t>
+          <t>108053</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>153550</t>
+          <t>154933</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>169682</t>
+          <t>171300</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>226571</t>
+          <t>229093</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>37026</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64628</t>
+          <t>65857</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>51850</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85375</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>96257</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>139525</t>
+          <t>138222</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>486010</t>
+          <t>527384</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>464057</t>
+          <t>504769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>505687</t>
+          <t>548057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>474096</t>
+          <t>516811</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454171</t>
+          <t>497326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>492080</t>
+          <t>535096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>960107</t>
+          <t>1044196</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>933302</t>
+          <t>1012925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>987806</t>
+          <t>1070504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -11767,67 +11767,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49893</t>
+          <t>56114</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38735</t>
+          <t>43994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63871</t>
+          <t>72031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>69828</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57562</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>83968</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65054</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54461</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76973</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114947</t>
+          <t>125942</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98502</t>
+          <t>109045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132925</t>
+          <t>147683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58252</t>
+          <t>63365</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>50116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73703</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87089</t>
+          <t>93142</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74313</t>
+          <t>81679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102319</t>
+          <t>107883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>145341</t>
+          <t>156507</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126668</t>
+          <t>138123</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164078</t>
+          <t>177167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>20374</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28413</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>51249</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>41635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>63053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -12106,17 +12106,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>26497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>40822</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>31656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>633541</t>
+          <t>688638</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>633541</t>
+          <t>688638</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633541</t>
+          <t>688638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>672892</t>
+          <t>730078</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672892</t>
+          <t>730078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>672892</t>
+          <t>730078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1306433</t>
+          <t>1418717</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1306433</t>
+          <t>1418717</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1306433</t>
+          <t>1418717</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1001671</t>
+          <t>835705</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>943957</t>
+          <t>805534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1101551</t>
+          <t>861962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>651832</t>
+          <t>732674</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>628125</t>
+          <t>706576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>675727</t>
+          <t>758106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1653503</t>
+          <t>1568379</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1578427</t>
+          <t>1531310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1834700</t>
+          <t>1606766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83815</t>
+          <t>92522</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40377</t>
+          <t>75867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>113738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>110160</t>
+          <t>119474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93574</t>
+          <t>104043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125625</t>
+          <t>137102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>193974</t>
+          <t>211995</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133217</t>
+          <t>187852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229514</t>
+          <t>238324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70488</t>
+          <t>81888</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36101</t>
+          <t>64866</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96501</t>
+          <t>102668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125203</t>
+          <t>140619</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106886</t>
+          <t>124545</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143296</t>
+          <t>160810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>195691</t>
+          <t>222508</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123079</t>
+          <t>197813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>231652</t>
+          <t>251266</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40625</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32179</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50873</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>58984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82219</t>
+          <t>86418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39352</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40667</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52986</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956812</t>
+          <t>1069446</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956812</t>
+          <t>1069446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956812</t>
+          <t>1069446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2149676</t>
+          <t>2118363</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2149676</t>
+          <t>2118363</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2149676</t>
+          <t>2118363</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>527833</t>
+          <t>605547</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>502731</t>
+          <t>576777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>550698</t>
+          <t>632689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>517067</t>
+          <t>567429</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224189</t>
+          <t>541638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>671201</t>
+          <t>590059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1044900</t>
+          <t>1172976</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>716975</t>
+          <t>1135293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1206129</t>
+          <t>1208491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,84%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76520</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94644</t>
+          <t>104630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>279382</t>
+          <t>81158</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90056</t>
+          <t>67772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>634370</t>
+          <t>98457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>355901</t>
+          <t>164096</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166030</t>
+          <t>142959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766490</t>
+          <t>188616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63424</t>
+          <t>67478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48745</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80412</t>
+          <t>86890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88458</t>
+          <t>107647</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>90568</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120308</t>
+          <t>126921</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>151882</t>
+          <t>175125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103615</t>
+          <t>150062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184004</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>31379</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>20755</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35012</t>
+          <t>45552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>47559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65622</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>25990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>41851</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>932951</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>932951</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>932951</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1637631</t>
+          <t>1614855</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1637631</t>
+          <t>1614855</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1637631</t>
+          <t>1614855</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>726882</t>
+          <t>780299</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>698452</t>
+          <t>754959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>748523</t>
+          <t>804720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>764040</t>
+          <t>760382</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>729561</t>
+          <t>731977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>825730</t>
+          <t>784715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1490923</t>
+          <t>1540681</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1448395</t>
+          <t>1498687</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1549914</t>
+          <t>1574459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>69390</t>
+          <t>73359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56370</t>
+          <t>58921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86507</t>
+          <t>90155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>118050</t>
+          <t>129054</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94564</t>
+          <t>110830</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136390</t>
+          <t>149742</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>187440</t>
+          <t>202414</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>162042</t>
+          <t>179009</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212408</t>
+          <t>227886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74033</t>
+          <t>78038</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59533</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91247</t>
+          <t>96103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>127082</t>
+          <t>133978</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>116082</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150597</t>
+          <t>153693</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>201115</t>
+          <t>212017</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172450</t>
+          <t>186255</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>230517</t>
+          <t>240201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40451</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>51358</t>
+          <t>56429</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39115</t>
+          <t>46002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64708</t>
+          <t>69978</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65846</t>
+          <t>71416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96488</t>
+          <t>103198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>40327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34403</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>49647</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,27 +14222,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>60427</t>
+          <t>66478</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>52645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77373</t>
+          <t>80732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925206</t>
+          <t>988461</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925206</t>
+          <t>988461</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925206</t>
+          <t>988461</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2020139</t>
+          <t>2107502</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2020139</t>
+          <t>2107502</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2020139</t>
+          <t>2107502</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2742397</t>
+          <t>2748935</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2671044</t>
+          <t>2695361</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2918715</t>
+          <t>2799901</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2407035</t>
+          <t>2577297</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1982924</t>
+          <t>2525143</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2571192</t>
+          <t>2625536</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5149433</t>
+          <t>5326233</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4627234</t>
+          <t>5251418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5366310</t>
+          <t>5391247</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>279617</t>
+          <t>304933</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>216712</t>
+          <t>270781</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>319419</t>
+          <t>337550</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>572645</t>
+          <t>399514</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>379350</t>
+          <t>368147</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1091992</t>
+          <t>433964</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>852262</t>
+          <t>704447</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>643970</t>
+          <t>657882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1530103</t>
+          <t>751283</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>266197</t>
+          <t>290770</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>204150</t>
+          <t>256670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>304368</t>
+          <t>327630</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>427831</t>
+          <t>475387</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>347715</t>
+          <t>442354</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>473990</t>
+          <t>509079</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>694028</t>
+          <t>766157</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>597898</t>
+          <t>720999</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>759706</t>
+          <t>823218</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>98180</t>
+          <t>107813</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74758</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119573</t>
+          <t>130171</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>145583</t>
+          <t>161754</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>118593</t>
+          <t>143815</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>170417</t>
+          <t>183378</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>243764</t>
+          <t>269566</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>210406</t>
+          <t>241154</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>278128</t>
+          <t>299597</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>76639</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>51577</t>
+          <t>60758</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>97541</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>104493</t>
+          <t>116396</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>81720</t>
+          <t>100259</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>120743</t>
+          <t>133219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>174393</t>
+          <t>193035</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>146578</t>
+          <t>169800</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>199342</t>
+          <t>220756</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
